--- a/New file upload/Traning report.xlsx
+++ b/New file upload/Traning report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="132" yWindow="528" windowWidth="22716" windowHeight="10524"/>
+    <workbookView xWindow="135" yWindow="525" windowWidth="20730" windowHeight="10530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6492" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6899" uniqueCount="666">
   <si>
     <t>ZONE NAME</t>
   </si>
@@ -2005,7 +2005,13 @@
     <t>2026-06-29 05:30:00</t>
   </si>
   <si>
-    <t>erp.developer8@kalabiz.com</t>
+    <t>Current status</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>left</t>
   </si>
 </sst>
 </file>
@@ -2029,12 +2035,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2050,9 +2062,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2394,10 +2407,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X408"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="22" width="26.6640625" customWidth="1"/>
-    <col min="24" max="24" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="22" width="26.7109375" customWidth="1"/>
+    <col min="24" max="24" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="12" x14ac:dyDescent="0.25">
@@ -2467,287 +2480,308 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="W1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="W2" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" ht="12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="W3" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="K4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" ht="12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="W4" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="K5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="W5" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="K6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U6" t="s">
+      <c r="U6" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="W6" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="G7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="K7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U7" t="s">
+      <c r="U7" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="12" x14ac:dyDescent="0.25">
@@ -2796,6 +2830,9 @@
       <c r="U8" t="s">
         <v>50</v>
       </c>
+      <c r="W8" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="9" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -2843,8 +2880,11 @@
       <c r="U9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W9" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2890,9 +2930,10 @@
       <c r="U10" t="s">
         <v>50</v>
       </c>
-      <c r="X10" s="1" t="s">
-        <v>663</v>
-      </c>
+      <c r="W10" t="s">
+        <v>664</v>
+      </c>
+      <c r="X10" s="1"/>
     </row>
     <row r="11" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -2940,6 +2981,9 @@
       <c r="U11" t="s">
         <v>50</v>
       </c>
+      <c r="W11" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="12" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -2987,6 +3031,9 @@
       <c r="U12" t="s">
         <v>50</v>
       </c>
+      <c r="W12" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="13" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -3034,6 +3081,9 @@
       <c r="U13" t="s">
         <v>50</v>
       </c>
+      <c r="W13" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="14" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3081,6 +3131,9 @@
       <c r="U14" t="s">
         <v>60</v>
       </c>
+      <c r="W14" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="15" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -3128,6 +3181,9 @@
       <c r="U15" t="s">
         <v>60</v>
       </c>
+      <c r="W15" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="16" spans="1:24" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -3175,8 +3231,11 @@
       <c r="U16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W16" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -3222,8 +3281,11 @@
       <c r="U17" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W17" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -3269,8 +3331,11 @@
       <c r="U18" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W18" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -3316,8 +3381,11 @@
       <c r="U19" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W19" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -3363,8 +3431,11 @@
       <c r="U20" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W20" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -3410,8 +3481,11 @@
       <c r="U21" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W21" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -3457,8 +3531,11 @@
       <c r="U22" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W22" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3504,8 +3581,11 @@
       <c r="U23" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W23" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -3551,8 +3631,11 @@
       <c r="U24" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W24" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -3598,8 +3681,11 @@
       <c r="U25" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W25" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3645,8 +3731,11 @@
       <c r="U26" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W26" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -3692,8 +3781,11 @@
       <c r="U27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="12" x14ac:dyDescent="0.25">
+      <c r="W27" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -3739,8 +3831,11 @@
       <c r="U28" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W28" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -3786,8 +3881,11 @@
       <c r="U29" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W29" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -3833,8 +3931,11 @@
       <c r="U30" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W30" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -3880,8 +3981,11 @@
       <c r="U31" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W31" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -3927,8 +4031,11 @@
       <c r="U32" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W32" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -3974,8 +4081,11 @@
       <c r="U33" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W33" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -4021,8 +4131,11 @@
       <c r="U34" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W34" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -4068,8 +4181,11 @@
       <c r="U35" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W35" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>22</v>
       </c>
@@ -4115,8 +4231,11 @@
       <c r="U36" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W36" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -4162,8 +4281,11 @@
       <c r="U37" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W37" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>22</v>
       </c>
@@ -4209,8 +4331,11 @@
       <c r="U38" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W38" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -4256,8 +4381,11 @@
       <c r="U39" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W39" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>22</v>
       </c>
@@ -4303,8 +4431,11 @@
       <c r="U40" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W40" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -4350,8 +4481,11 @@
       <c r="U41" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W41" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -4397,8 +4531,11 @@
       <c r="U42" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W42" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -4444,8 +4581,11 @@
       <c r="U43" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W43" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -4491,8 +4631,11 @@
       <c r="U44" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W44" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -4538,8 +4681,11 @@
       <c r="U45" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W45" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -4585,8 +4731,11 @@
       <c r="U46" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W46" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -4632,8 +4781,11 @@
       <c r="U47" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W47" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -4679,8 +4831,11 @@
       <c r="U48" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W48" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -4726,8 +4881,11 @@
       <c r="U49" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W49" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>22</v>
       </c>
@@ -4773,8 +4931,11 @@
       <c r="U50" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W50" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -4820,8 +4981,11 @@
       <c r="U51" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W51" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>22</v>
       </c>
@@ -4867,8 +5031,11 @@
       <c r="U52" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W52" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="U53" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W53" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -4961,8 +5131,11 @@
       <c r="U54" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W54" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -5008,8 +5181,11 @@
       <c r="U55" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W55" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -5055,8 +5231,11 @@
       <c r="U56" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W56" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -5102,8 +5281,11 @@
       <c r="U57" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W57" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -5149,8 +5331,11 @@
       <c r="U58" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W58" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -5199,8 +5384,11 @@
       <c r="U59" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W59" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -5246,8 +5434,11 @@
       <c r="U60" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W60" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>22</v>
       </c>
@@ -5293,8 +5484,11 @@
       <c r="U61" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W61" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>22</v>
       </c>
@@ -5340,8 +5534,11 @@
       <c r="U62" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W62" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>22</v>
       </c>
@@ -5387,8 +5584,11 @@
       <c r="U63" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W63" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>22</v>
       </c>
@@ -5434,8 +5634,11 @@
       <c r="U64" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W64" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>22</v>
       </c>
@@ -5481,8 +5684,11 @@
       <c r="U65" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W65" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>22</v>
       </c>
@@ -5528,8 +5734,11 @@
       <c r="U66" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W66" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>22</v>
       </c>
@@ -5575,8 +5784,11 @@
       <c r="U67" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W67" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>22</v>
       </c>
@@ -5622,8 +5834,11 @@
       <c r="U68" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W68" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>22</v>
       </c>
@@ -5669,8 +5884,11 @@
       <c r="U69" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W69" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>22</v>
       </c>
@@ -5716,8 +5934,11 @@
       <c r="U70" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W70" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>22</v>
       </c>
@@ -5763,8 +5984,11 @@
       <c r="U71" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W71" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>22</v>
       </c>
@@ -5810,8 +6034,11 @@
       <c r="U72" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W72" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>22</v>
       </c>
@@ -5857,8 +6084,11 @@
       <c r="U73" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W73" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>22</v>
       </c>
@@ -5904,8 +6134,11 @@
       <c r="U74" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W74" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>22</v>
       </c>
@@ -5951,8 +6184,11 @@
       <c r="U75" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W75" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -5998,8 +6234,11 @@
       <c r="U76" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W76" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>22</v>
       </c>
@@ -6045,8 +6284,11 @@
       <c r="U77" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W77" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>22</v>
       </c>
@@ -6092,8 +6334,11 @@
       <c r="U78" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W78" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>22</v>
       </c>
@@ -6127,8 +6372,11 @@
       <c r="U79" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W79" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>22</v>
       </c>
@@ -6174,8 +6422,11 @@
       <c r="U80" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W80" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>22</v>
       </c>
@@ -6221,8 +6472,11 @@
       <c r="U81" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W81" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -6268,8 +6522,11 @@
       <c r="U82" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W82" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>22</v>
       </c>
@@ -6318,8 +6575,11 @@
       <c r="U83" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W83" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>22</v>
       </c>
@@ -6368,8 +6628,11 @@
       <c r="U84" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W84" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>22</v>
       </c>
@@ -6415,8 +6678,11 @@
       <c r="U85" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W85" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>22</v>
       </c>
@@ -6462,8 +6728,11 @@
       <c r="U86" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W86" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>22</v>
       </c>
@@ -6509,8 +6778,11 @@
       <c r="U87" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W87" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>22</v>
       </c>
@@ -6559,8 +6831,11 @@
       <c r="U88" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W88" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>22</v>
       </c>
@@ -6609,8 +6884,11 @@
       <c r="U89" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W89" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>22</v>
       </c>
@@ -6656,8 +6934,11 @@
       <c r="U90" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W90" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>22</v>
       </c>
@@ -6706,8 +6987,11 @@
       <c r="U91" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W91" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>22</v>
       </c>
@@ -6756,8 +7040,11 @@
       <c r="U92" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W92" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>22</v>
       </c>
@@ -6803,8 +7090,11 @@
       <c r="U93" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W93" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>22</v>
       </c>
@@ -6850,8 +7140,11 @@
       <c r="U94" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W94" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>22</v>
       </c>
@@ -6900,8 +7193,11 @@
       <c r="U95" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W95" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>22</v>
       </c>
@@ -6950,8 +7246,11 @@
       <c r="U96" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W96" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>22</v>
       </c>
@@ -6997,8 +7296,11 @@
       <c r="U97" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W97" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>22</v>
       </c>
@@ -7044,8 +7346,11 @@
       <c r="U98" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W98" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>22</v>
       </c>
@@ -7091,8 +7396,11 @@
       <c r="U99" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W99" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>22</v>
       </c>
@@ -7138,8 +7446,11 @@
       <c r="U100" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W100" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>22</v>
       </c>
@@ -7185,8 +7496,11 @@
       <c r="U101" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W101" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>22</v>
       </c>
@@ -7232,8 +7546,11 @@
       <c r="U102" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W102" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -7279,8 +7596,11 @@
       <c r="U103" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W103" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>22</v>
       </c>
@@ -7326,8 +7646,11 @@
       <c r="U104" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W104" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -7373,8 +7696,11 @@
       <c r="U105" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W105" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -7420,8 +7746,11 @@
       <c r="U106" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W106" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -7467,8 +7796,11 @@
       <c r="U107" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W107" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -7514,8 +7846,11 @@
       <c r="U108" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W108" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -7561,8 +7896,11 @@
       <c r="U109" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W109" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -7608,8 +7946,11 @@
       <c r="U110" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W110" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>22</v>
       </c>
@@ -7655,8 +7996,11 @@
       <c r="U111" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W111" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>22</v>
       </c>
@@ -7702,8 +8046,11 @@
       <c r="U112" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W112" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>22</v>
       </c>
@@ -7749,8 +8096,11 @@
       <c r="U113" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W113" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>22</v>
       </c>
@@ -7796,8 +8146,11 @@
       <c r="U114" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W114" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>22</v>
       </c>
@@ -7843,8 +8196,11 @@
       <c r="U115" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W115" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>22</v>
       </c>
@@ -7890,8 +8246,11 @@
       <c r="U116" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W116" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>22</v>
       </c>
@@ -7937,8 +8296,11 @@
       <c r="U117" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W117" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -7984,8 +8346,11 @@
       <c r="U118" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W118" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>22</v>
       </c>
@@ -8031,8 +8396,11 @@
       <c r="U119" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W119" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>22</v>
       </c>
@@ -8078,8 +8446,11 @@
       <c r="U120" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W120" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>22</v>
       </c>
@@ -8125,8 +8496,11 @@
       <c r="U121" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W121" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>22</v>
       </c>
@@ -8172,8 +8546,11 @@
       <c r="U122" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W122" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>22</v>
       </c>
@@ -8219,8 +8596,11 @@
       <c r="U123" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W123" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>22</v>
       </c>
@@ -8254,8 +8634,11 @@
       <c r="U124" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W124" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>22</v>
       </c>
@@ -8301,8 +8684,11 @@
       <c r="U125" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W125" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>22</v>
       </c>
@@ -8348,8 +8734,11 @@
       <c r="U126" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W126" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>22</v>
       </c>
@@ -8395,8 +8784,11 @@
       <c r="U127" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W127" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>22</v>
       </c>
@@ -8442,8 +8834,11 @@
       <c r="U128" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W128" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>22</v>
       </c>
@@ -8489,8 +8884,11 @@
       <c r="U129" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W129" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>22</v>
       </c>
@@ -8536,8 +8934,11 @@
       <c r="U130" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W130" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>22</v>
       </c>
@@ -8583,8 +8984,11 @@
       <c r="U131" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W131" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>22</v>
       </c>
@@ -8630,8 +9034,11 @@
       <c r="U132" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W132" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>22</v>
       </c>
@@ -8677,8 +9084,11 @@
       <c r="U133" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W133" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>22</v>
       </c>
@@ -8724,8 +9134,11 @@
       <c r="U134" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W134" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>22</v>
       </c>
@@ -8771,8 +9184,11 @@
       <c r="U135" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W135" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>22</v>
       </c>
@@ -8818,8 +9234,11 @@
       <c r="U136" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W136" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>22</v>
       </c>
@@ -8865,8 +9284,11 @@
       <c r="U137" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W137" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>22</v>
       </c>
@@ -8912,8 +9334,11 @@
       <c r="U138" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W138" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>22</v>
       </c>
@@ -8959,8 +9384,11 @@
       <c r="U139" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W139" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>22</v>
       </c>
@@ -9006,8 +9434,11 @@
       <c r="U140" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W140" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>22</v>
       </c>
@@ -9053,8 +9484,11 @@
       <c r="U141" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W141" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>22</v>
       </c>
@@ -9103,8 +9537,11 @@
       <c r="U142" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W142" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>22</v>
       </c>
@@ -9153,8 +9590,11 @@
       <c r="U143" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W143" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>22</v>
       </c>
@@ -9200,8 +9640,11 @@
       <c r="U144" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W144" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>22</v>
       </c>
@@ -9247,8 +9690,11 @@
       <c r="U145" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W145" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>22</v>
       </c>
@@ -9294,8 +9740,11 @@
       <c r="U146" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W146" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>22</v>
       </c>
@@ -9341,8 +9790,11 @@
       <c r="U147" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W147" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>22</v>
       </c>
@@ -9388,8 +9840,11 @@
       <c r="U148" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W148" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>22</v>
       </c>
@@ -9438,8 +9893,11 @@
       <c r="U149" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W149" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>22</v>
       </c>
@@ -9488,8 +9946,11 @@
       <c r="U150" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W150" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>22</v>
       </c>
@@ -9535,8 +9996,11 @@
       <c r="U151" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W151" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>22</v>
       </c>
@@ -9582,8 +10046,11 @@
       <c r="U152" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W152" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>22</v>
       </c>
@@ -9629,8 +10096,11 @@
       <c r="U153" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W153" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>22</v>
       </c>
@@ -9676,8 +10146,11 @@
       <c r="U154" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W154" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>22</v>
       </c>
@@ -9723,8 +10196,11 @@
       <c r="U155" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W155" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>22</v>
       </c>
@@ -9770,8 +10246,11 @@
       <c r="U156" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W156" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>22</v>
       </c>
@@ -9817,8 +10296,11 @@
       <c r="U157" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W157" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>22</v>
       </c>
@@ -9864,8 +10346,11 @@
       <c r="U158" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W158" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>22</v>
       </c>
@@ -9911,8 +10396,11 @@
       <c r="U159" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W159" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>22</v>
       </c>
@@ -9958,8 +10446,11 @@
       <c r="U160" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W160" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>22</v>
       </c>
@@ -10005,8 +10496,11 @@
       <c r="U161" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W161" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>22</v>
       </c>
@@ -10052,8 +10546,11 @@
       <c r="U162" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W162" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>22</v>
       </c>
@@ -10099,8 +10596,11 @@
       <c r="U163" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W163" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>22</v>
       </c>
@@ -10146,8 +10646,11 @@
       <c r="U164" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W164" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>22</v>
       </c>
@@ -10196,8 +10699,11 @@
       <c r="U165" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W165" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>22</v>
       </c>
@@ -10246,8 +10752,11 @@
       <c r="U166" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W166" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>22</v>
       </c>
@@ -10293,8 +10802,11 @@
       <c r="U167" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W167" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>22</v>
       </c>
@@ -10340,8 +10852,11 @@
       <c r="U168" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W168" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>22</v>
       </c>
@@ -10387,8 +10902,11 @@
       <c r="U169" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W169" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>22</v>
       </c>
@@ -10434,8 +10952,11 @@
       <c r="U170" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W170" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>22</v>
       </c>
@@ -10481,8 +11002,11 @@
       <c r="U171" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W171" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>22</v>
       </c>
@@ -10528,8 +11052,11 @@
       <c r="U172" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W172" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>22</v>
       </c>
@@ -10575,8 +11102,11 @@
       <c r="U173" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W173" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>22</v>
       </c>
@@ -10622,8 +11152,11 @@
       <c r="U174" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W174" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>22</v>
       </c>
@@ -10669,8 +11202,11 @@
       <c r="U175" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W175" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>22</v>
       </c>
@@ -10716,8 +11252,11 @@
       <c r="U176" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W176" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>22</v>
       </c>
@@ -10763,8 +11302,11 @@
       <c r="U177" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W177" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>22</v>
       </c>
@@ -10810,8 +11352,11 @@
       <c r="U178" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W178" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>22</v>
       </c>
@@ -10857,8 +11402,11 @@
       <c r="U179" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W179" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>22</v>
       </c>
@@ -10904,8 +11452,11 @@
       <c r="U180" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W180" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>22</v>
       </c>
@@ -10954,8 +11505,11 @@
       <c r="U181" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W181" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>22</v>
       </c>
@@ -11004,8 +11558,11 @@
       <c r="U182" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W182" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>22</v>
       </c>
@@ -11051,8 +11608,11 @@
       <c r="U183" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W183" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>22</v>
       </c>
@@ -11098,8 +11658,11 @@
       <c r="U184" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W184" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>22</v>
       </c>
@@ -11145,8 +11708,11 @@
       <c r="U185" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W185" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -11195,8 +11761,11 @@
       <c r="U186" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W186" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -11245,8 +11814,11 @@
       <c r="U187" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W187" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>22</v>
       </c>
@@ -11292,8 +11864,11 @@
       <c r="U188" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W188" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>22</v>
       </c>
@@ -11342,8 +11917,11 @@
       <c r="U189" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W189" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -11392,8 +11970,11 @@
       <c r="U190" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W190" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>22</v>
       </c>
@@ -11442,8 +12023,11 @@
       <c r="U191" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W191" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>22</v>
       </c>
@@ -11492,8 +12076,11 @@
       <c r="U192" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W192" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>22</v>
       </c>
@@ -11539,8 +12126,11 @@
       <c r="U193" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W193" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>22</v>
       </c>
@@ -11589,8 +12179,11 @@
       <c r="U194" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W194" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>22</v>
       </c>
@@ -11639,8 +12232,11 @@
       <c r="U195" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W195" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>22</v>
       </c>
@@ -11686,8 +12282,11 @@
       <c r="U196" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W196" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>22</v>
       </c>
@@ -11736,8 +12335,11 @@
       <c r="U197" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W197" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>22</v>
       </c>
@@ -11786,8 +12388,11 @@
       <c r="U198" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W198" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>22</v>
       </c>
@@ -11836,8 +12441,11 @@
       <c r="U199" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W199" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>22</v>
       </c>
@@ -11883,8 +12491,11 @@
       <c r="U200" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W200" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>22</v>
       </c>
@@ -11930,8 +12541,11 @@
       <c r="U201" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W201" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>22</v>
       </c>
@@ -11977,8 +12591,11 @@
       <c r="U202" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W202" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>22</v>
       </c>
@@ -12024,8 +12641,11 @@
       <c r="U203" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W203" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>22</v>
       </c>
@@ -12071,8 +12691,11 @@
       <c r="U204" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W204" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>22</v>
       </c>
@@ -12118,8 +12741,11 @@
       <c r="U205" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W205" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>22</v>
       </c>
@@ -12165,8 +12791,11 @@
       <c r="U206" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W206" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>22</v>
       </c>
@@ -12212,8 +12841,11 @@
       <c r="U207" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W207" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>22</v>
       </c>
@@ -12259,8 +12891,11 @@
       <c r="U208" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W208" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>22</v>
       </c>
@@ -12294,8 +12929,11 @@
       <c r="U209" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W209" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>22</v>
       </c>
@@ -12341,8 +12979,11 @@
       <c r="U210" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W210" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>22</v>
       </c>
@@ -12388,8 +13029,11 @@
       <c r="U211" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W211" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>22</v>
       </c>
@@ -12435,8 +13079,11 @@
       <c r="U212" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W212" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>22</v>
       </c>
@@ -12482,8 +13129,11 @@
       <c r="U213" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W213" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>22</v>
       </c>
@@ -12529,8 +13179,11 @@
       <c r="U214" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W214" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>22</v>
       </c>
@@ -12576,8 +13229,11 @@
       <c r="U215" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W215" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>22</v>
       </c>
@@ -12623,8 +13279,11 @@
       <c r="U216" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W216" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>22</v>
       </c>
@@ -12670,8 +13329,11 @@
       <c r="U217" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W217" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>22</v>
       </c>
@@ -12717,8 +13379,11 @@
       <c r="U218" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W218" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>22</v>
       </c>
@@ -12764,8 +13429,11 @@
       <c r="U219" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W219" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>22</v>
       </c>
@@ -12811,8 +13479,11 @@
       <c r="U220" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W220" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>22</v>
       </c>
@@ -12858,8 +13529,11 @@
       <c r="U221" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W221" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>22</v>
       </c>
@@ -12905,8 +13579,11 @@
       <c r="U222" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W222" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>22</v>
       </c>
@@ -12952,8 +13629,11 @@
       <c r="U223" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W223" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>22</v>
       </c>
@@ -12999,8 +13679,11 @@
       <c r="U224" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W224" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>22</v>
       </c>
@@ -13046,8 +13729,11 @@
       <c r="U225" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W225" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>22</v>
       </c>
@@ -13093,8 +13779,11 @@
       <c r="U226" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W226" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>22</v>
       </c>
@@ -13140,8 +13829,11 @@
       <c r="U227" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W227" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>22</v>
       </c>
@@ -13187,8 +13879,11 @@
       <c r="U228" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W228" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>22</v>
       </c>
@@ -13234,8 +13929,11 @@
       <c r="U229" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W229" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>22</v>
       </c>
@@ -13281,8 +13979,11 @@
       <c r="U230" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W230" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>22</v>
       </c>
@@ -13328,8 +14029,11 @@
       <c r="U231" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W231" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>22</v>
       </c>
@@ -13375,8 +14079,11 @@
       <c r="U232" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W232" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>22</v>
       </c>
@@ -13422,8 +14129,11 @@
       <c r="U233" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W233" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>22</v>
       </c>
@@ -13469,8 +14179,11 @@
       <c r="U234" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W234" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>22</v>
       </c>
@@ -13516,8 +14229,11 @@
       <c r="U235" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W235" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>22</v>
       </c>
@@ -13563,8 +14279,11 @@
       <c r="U236" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W236" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>22</v>
       </c>
@@ -13610,8 +14329,11 @@
       <c r="U237" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W237" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>22</v>
       </c>
@@ -13657,8 +14379,11 @@
       <c r="U238" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W238" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>22</v>
       </c>
@@ -13704,8 +14429,11 @@
       <c r="U239" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W239" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>22</v>
       </c>
@@ -13751,8 +14479,11 @@
       <c r="U240" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W240" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>22</v>
       </c>
@@ -13798,8 +14529,11 @@
       <c r="U241" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W241" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>22</v>
       </c>
@@ -13845,8 +14579,11 @@
       <c r="U242" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W242" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>22</v>
       </c>
@@ -13892,8 +14629,11 @@
       <c r="U243" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W243" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>22</v>
       </c>
@@ -13939,8 +14679,11 @@
       <c r="U244" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W244" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>22</v>
       </c>
@@ -13986,8 +14729,11 @@
       <c r="U245" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W245" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>22</v>
       </c>
@@ -14033,8 +14779,11 @@
       <c r="U246" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W246" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>22</v>
       </c>
@@ -14080,8 +14829,11 @@
       <c r="U247" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W247" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>22</v>
       </c>
@@ -14127,8 +14879,11 @@
       <c r="U248" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W248" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>22</v>
       </c>
@@ -14174,8 +14929,11 @@
       <c r="U249" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W249" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>22</v>
       </c>
@@ -14221,8 +14979,11 @@
       <c r="U250" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W250" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>22</v>
       </c>
@@ -14271,8 +15032,11 @@
       <c r="U251" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W251" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>22</v>
       </c>
@@ -14318,8 +15082,11 @@
       <c r="U252" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W252" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>22</v>
       </c>
@@ -14365,8 +15132,11 @@
       <c r="U253" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W253" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>22</v>
       </c>
@@ -14415,8 +15185,11 @@
       <c r="U254" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W254" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>22</v>
       </c>
@@ -14465,8 +15238,11 @@
       <c r="U255" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W255" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>22</v>
       </c>
@@ -14512,8 +15288,11 @@
       <c r="U256" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W256" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>22</v>
       </c>
@@ -14559,8 +15338,11 @@
       <c r="U257" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W257" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -14606,8 +15388,11 @@
       <c r="U258" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W258" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>22</v>
       </c>
@@ -14653,8 +15438,11 @@
       <c r="U259" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W259" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>22</v>
       </c>
@@ -14700,8 +15488,11 @@
       <c r="U260" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W260" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>22</v>
       </c>
@@ -14747,8 +15538,11 @@
       <c r="U261" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W261" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>22</v>
       </c>
@@ -14794,8 +15588,11 @@
       <c r="U262" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W262" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>22</v>
       </c>
@@ -14841,8 +15638,11 @@
       <c r="U263" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W263" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>22</v>
       </c>
@@ -14888,8 +15688,11 @@
       <c r="U264" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W264" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>22</v>
       </c>
@@ -14935,8 +15738,11 @@
       <c r="U265" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W265" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>22</v>
       </c>
@@ -14982,8 +15788,11 @@
       <c r="U266" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W266" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>22</v>
       </c>
@@ -15029,8 +15838,11 @@
       <c r="U267" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W267" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>22</v>
       </c>
@@ -15076,8 +15888,11 @@
       <c r="U268" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W268" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>22</v>
       </c>
@@ -15123,8 +15938,11 @@
       <c r="U269" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W269" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>22</v>
       </c>
@@ -15170,8 +15988,11 @@
       <c r="U270" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W270" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>22</v>
       </c>
@@ -15217,8 +16038,11 @@
       <c r="U271" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W271" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>22</v>
       </c>
@@ -15264,8 +16088,11 @@
       <c r="U272" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W272" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>22</v>
       </c>
@@ -15311,8 +16138,11 @@
       <c r="U273" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W273" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>22</v>
       </c>
@@ -15358,8 +16188,11 @@
       <c r="U274" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W274" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>22</v>
       </c>
@@ -15405,8 +16238,11 @@
       <c r="U275" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W275" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>22</v>
       </c>
@@ -15452,8 +16288,11 @@
       <c r="U276" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W276" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>22</v>
       </c>
@@ -15499,8 +16338,11 @@
       <c r="U277" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W277" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>22</v>
       </c>
@@ -15546,8 +16388,11 @@
       <c r="U278" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W278" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>22</v>
       </c>
@@ -15596,8 +16441,11 @@
       <c r="U279" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W279" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>22</v>
       </c>
@@ -15646,8 +16494,11 @@
       <c r="U280" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W280" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>22</v>
       </c>
@@ -15693,8 +16544,11 @@
       <c r="U281" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W281" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>22</v>
       </c>
@@ -15740,8 +16594,11 @@
       <c r="U282" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W282" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>22</v>
       </c>
@@ -15790,8 +16647,11 @@
       <c r="U283" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W283" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>22</v>
       </c>
@@ -15840,8 +16700,11 @@
       <c r="U284" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W284" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>22</v>
       </c>
@@ -15887,8 +16750,11 @@
       <c r="U285" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W285" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>22</v>
       </c>
@@ -15922,8 +16788,11 @@
       <c r="U286" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="287" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W286" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>22</v>
       </c>
@@ -15972,8 +16841,11 @@
       <c r="U287" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W287" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>22</v>
       </c>
@@ -16022,8 +16894,11 @@
       <c r="U288" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="289" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W288" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>22</v>
       </c>
@@ -16069,8 +16944,11 @@
       <c r="U289" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="290" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W289" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>22</v>
       </c>
@@ -16116,8 +16994,11 @@
       <c r="U290" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="291" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W290" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>22</v>
       </c>
@@ -16166,8 +17047,11 @@
       <c r="U291" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="292" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W291" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>22</v>
       </c>
@@ -16216,8 +17100,11 @@
       <c r="U292" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="293" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W292" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>22</v>
       </c>
@@ -16266,8 +17153,11 @@
       <c r="U293" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="294" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W293" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>22</v>
       </c>
@@ -16316,8 +17206,11 @@
       <c r="U294" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="295" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W294" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>22</v>
       </c>
@@ -16366,8 +17259,11 @@
       <c r="U295" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="296" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W295" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>22</v>
       </c>
@@ -16416,8 +17312,11 @@
       <c r="U296" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="297" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W296" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>22</v>
       </c>
@@ -16463,8 +17362,11 @@
       <c r="U297" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="298" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W297" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>22</v>
       </c>
@@ -16513,8 +17415,11 @@
       <c r="U298" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="299" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W298" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>22</v>
       </c>
@@ -16563,8 +17468,11 @@
       <c r="U299" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="300" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W299" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>22</v>
       </c>
@@ -16631,8 +17539,11 @@
       <c r="V300" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="301" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W300" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>22</v>
       </c>
@@ -16699,8 +17610,11 @@
       <c r="V301" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="302" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W301" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>22</v>
       </c>
@@ -16764,8 +17678,11 @@
       <c r="V302" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="303" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W302" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>22</v>
       </c>
@@ -16829,8 +17746,11 @@
       <c r="V303" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="304" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W303" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>22</v>
       </c>
@@ -16894,8 +17814,11 @@
       <c r="V304" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="305" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W304" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>22</v>
       </c>
@@ -16962,8 +17885,11 @@
       <c r="V305" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="306" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W305" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>22</v>
       </c>
@@ -17027,8 +17953,11 @@
       <c r="V306" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="307" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W306" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>22</v>
       </c>
@@ -17092,8 +18021,11 @@
       <c r="V307" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="308" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W307" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>22</v>
       </c>
@@ -17157,8 +18089,11 @@
       <c r="V308" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="309" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W308" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="309" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>22</v>
       </c>
@@ -17222,8 +18157,11 @@
       <c r="V309" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="310" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W309" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="310" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>22</v>
       </c>
@@ -17287,8 +18225,11 @@
       <c r="V310" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="311" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W310" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="311" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>22</v>
       </c>
@@ -17352,8 +18293,11 @@
       <c r="V311" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="312" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W311" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="312" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>22</v>
       </c>
@@ -17417,8 +18361,11 @@
       <c r="V312" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="313" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W312" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="313" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>22</v>
       </c>
@@ -17482,8 +18429,11 @@
       <c r="V313" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="314" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W313" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="314" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>22</v>
       </c>
@@ -17547,8 +18497,11 @@
       <c r="V314" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="315" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W314" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="315" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>22</v>
       </c>
@@ -17612,8 +18565,11 @@
       <c r="V315" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="316" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W315" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="316" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>22</v>
       </c>
@@ -17677,8 +18633,11 @@
       <c r="V316" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="317" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W316" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="317" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>22</v>
       </c>
@@ -17742,8 +18701,11 @@
       <c r="V317" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="318" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W317" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="318" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>22</v>
       </c>
@@ -17807,8 +18769,11 @@
       <c r="V318" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="319" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W318" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="319" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>22</v>
       </c>
@@ -17872,8 +18837,11 @@
       <c r="V319" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="320" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W319" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="320" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>22</v>
       </c>
@@ -17940,8 +18908,11 @@
       <c r="V320" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="321" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W320" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="321" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>22</v>
       </c>
@@ -18008,8 +18979,11 @@
       <c r="V321" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="322" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W321" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>22</v>
       </c>
@@ -18076,8 +19050,11 @@
       <c r="V322" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="323" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W322" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="323" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>22</v>
       </c>
@@ -18144,8 +19121,11 @@
       <c r="V323" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="324" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W323" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="324" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>22</v>
       </c>
@@ -18212,8 +19192,11 @@
       <c r="V324" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="325" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W324" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="325" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>22</v>
       </c>
@@ -18280,8 +19263,11 @@
       <c r="V325" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="326" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W325" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="326" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>22</v>
       </c>
@@ -18342,8 +19328,11 @@
       <c r="U326" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="327" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W326" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="327" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>22</v>
       </c>
@@ -18404,8 +19393,11 @@
       <c r="U327" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="328" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W327" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="328" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>22</v>
       </c>
@@ -18469,8 +19461,11 @@
       <c r="V328" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="329" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W328" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="329" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>22</v>
       </c>
@@ -18534,8 +19529,11 @@
       <c r="V329" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="330" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W329" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="330" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>22</v>
       </c>
@@ -18584,8 +19582,11 @@
       <c r="U330" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="331" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W330" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="331" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>22</v>
       </c>
@@ -18634,8 +19635,11 @@
       <c r="U331" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="332" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W331" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="332" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>22</v>
       </c>
@@ -18684,8 +19688,11 @@
       <c r="U332" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="333" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W332" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="333" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>22</v>
       </c>
@@ -18734,8 +19741,11 @@
       <c r="U333" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="334" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W333" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="334" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>22</v>
       </c>
@@ -18784,8 +19794,11 @@
       <c r="U334" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="335" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W334" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="335" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>22</v>
       </c>
@@ -18834,8 +19847,11 @@
       <c r="U335" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="336" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W335" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="336" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>22</v>
       </c>
@@ -18884,8 +19900,11 @@
       <c r="U336" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="337" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W336" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="337" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>22</v>
       </c>
@@ -18934,8 +19953,11 @@
       <c r="U337" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="338" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W337" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="338" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>22</v>
       </c>
@@ -18984,8 +20006,11 @@
       <c r="U338" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="339" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W338" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="339" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>22</v>
       </c>
@@ -19034,8 +20059,11 @@
       <c r="U339" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="340" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W339" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="340" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>22</v>
       </c>
@@ -19084,8 +20112,11 @@
       <c r="U340" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="341" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W340" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="341" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>22</v>
       </c>
@@ -19134,8 +20165,11 @@
       <c r="U341" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="342" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W341" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="342" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>22</v>
       </c>
@@ -19184,8 +20218,11 @@
       <c r="U342" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="343" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W342" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="343" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>22</v>
       </c>
@@ -19231,8 +20268,11 @@
       <c r="U343" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="344" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W343" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="344" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>22</v>
       </c>
@@ -19281,8 +20321,11 @@
       <c r="U344" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="345" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W344" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="345" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>22</v>
       </c>
@@ -19328,8 +20371,11 @@
       <c r="U345" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="346" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W345" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="346" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>22</v>
       </c>
@@ -19378,8 +20424,11 @@
       <c r="U346" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="347" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W346" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="347" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>22</v>
       </c>
@@ -19428,8 +20477,11 @@
       <c r="U347" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="348" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W347" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="348" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>22</v>
       </c>
@@ -19478,8 +20530,11 @@
       <c r="U348" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="349" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W348" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="349" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>22</v>
       </c>
@@ -19528,8 +20583,11 @@
       <c r="U349" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="350" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W349" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="350" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>22</v>
       </c>
@@ -19563,8 +20621,11 @@
       <c r="U350" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="351" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W350" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="351" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>22</v>
       </c>
@@ -19616,8 +20677,11 @@
       <c r="V351" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="352" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W351" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="352" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>22</v>
       </c>
@@ -19684,8 +20748,11 @@
       <c r="V352" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="353" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W352" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="353" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>22</v>
       </c>
@@ -19752,8 +20819,11 @@
       <c r="V353" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="354" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W353" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="354" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>22</v>
       </c>
@@ -19817,8 +20887,11 @@
       <c r="V354" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="355" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W354" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="355" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>22</v>
       </c>
@@ -19885,8 +20958,11 @@
       <c r="V355" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="356" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W355" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="356" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>22</v>
       </c>
@@ -19950,8 +21026,11 @@
       <c r="V356" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="357" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W356" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="357" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>22</v>
       </c>
@@ -20018,8 +21097,11 @@
       <c r="V357" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="358" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W357" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="358" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>22</v>
       </c>
@@ -20068,8 +21150,11 @@
       <c r="U358" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="359" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W358" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="359" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>22</v>
       </c>
@@ -20118,8 +21203,11 @@
       <c r="U359" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="360" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W359" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="360" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>22</v>
       </c>
@@ -20186,8 +21274,11 @@
       <c r="V360" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="361" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W360" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="361" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>22</v>
       </c>
@@ -20254,8 +21345,11 @@
       <c r="V361" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="362" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W361" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="362" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>22</v>
       </c>
@@ -20319,8 +21413,11 @@
       <c r="V362" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="363" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W362" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="363" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>22</v>
       </c>
@@ -20387,8 +21484,11 @@
       <c r="V363" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="364" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W363" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="364" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>22</v>
       </c>
@@ -20455,8 +21555,11 @@
       <c r="V364" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="365" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W364" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="365" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>22</v>
       </c>
@@ -20523,8 +21626,11 @@
       <c r="V365" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="366" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W365" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="366" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>22</v>
       </c>
@@ -20591,8 +21697,11 @@
       <c r="V366" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="367" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W366" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="367" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>22</v>
       </c>
@@ -20656,8 +21765,11 @@
       <c r="V367" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="368" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W367" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="368" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>22</v>
       </c>
@@ -20709,8 +21821,11 @@
       <c r="V368" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="369" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W368" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="369" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>22</v>
       </c>
@@ -20774,8 +21889,11 @@
       <c r="V369" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="370" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W369" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="370" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>22</v>
       </c>
@@ -20839,8 +21957,11 @@
       <c r="V370" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="371" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W370" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="371" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>22</v>
       </c>
@@ -20907,8 +22028,11 @@
       <c r="V371" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="372" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W371" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="372" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>22</v>
       </c>
@@ -20975,8 +22099,11 @@
       <c r="V372" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="373" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W372" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="373" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>22</v>
       </c>
@@ -21040,8 +22167,11 @@
       <c r="V373" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="374" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W373" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="374" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>22</v>
       </c>
@@ -21105,8 +22235,11 @@
       <c r="V374" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="375" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W374" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="375" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>22</v>
       </c>
@@ -21173,8 +22306,11 @@
       <c r="V375" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="376" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W375" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="376" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>22</v>
       </c>
@@ -21241,8 +22377,11 @@
       <c r="V376" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="377" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W376" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="377" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>22</v>
       </c>
@@ -21306,8 +22445,11 @@
       <c r="U377" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="378" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W377" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="378" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>22</v>
       </c>
@@ -21356,8 +22498,11 @@
       <c r="U378" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="379" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W378" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="379" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>22</v>
       </c>
@@ -21406,8 +22551,11 @@
       <c r="U379" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="380" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W379" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="380" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>22</v>
       </c>
@@ -21471,8 +22619,11 @@
       <c r="V380" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="381" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W380" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="381" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>22</v>
       </c>
@@ -21536,8 +22687,11 @@
       <c r="V381" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="382" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W381" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="382" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>22</v>
       </c>
@@ -21583,8 +22737,11 @@
       <c r="U382" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="383" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W382" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="383" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>22</v>
       </c>
@@ -21630,8 +22787,11 @@
       <c r="U383" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="384" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W383" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="384" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>22</v>
       </c>
@@ -21677,8 +22837,11 @@
       <c r="U384" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="385" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W384" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="385" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>22</v>
       </c>
@@ -21724,8 +22887,11 @@
       <c r="U385" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="386" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W385" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="386" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>22</v>
       </c>
@@ -21759,8 +22925,11 @@
       <c r="U386" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="387" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W386" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="387" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>22</v>
       </c>
@@ -21806,8 +22975,11 @@
       <c r="U387" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="388" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W387" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="388" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>22</v>
       </c>
@@ -21856,8 +23028,11 @@
       <c r="U388" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="389" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W388" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="389" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>22</v>
       </c>
@@ -21891,8 +23066,11 @@
       <c r="U389" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="390" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W389" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="390" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>22</v>
       </c>
@@ -21926,8 +23104,11 @@
       <c r="U390" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="391" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W390" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="391" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>22</v>
       </c>
@@ -21973,8 +23154,11 @@
       <c r="U391" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="392" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W391" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="392" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>22</v>
       </c>
@@ -22023,8 +23207,11 @@
       <c r="U392" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="393" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W392" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="393" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>22</v>
       </c>
@@ -22058,8 +23245,11 @@
       <c r="U393" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="394" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W393" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="394" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>22</v>
       </c>
@@ -22108,8 +23298,11 @@
       <c r="U394" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="395" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W394" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="395" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>22</v>
       </c>
@@ -22158,8 +23351,11 @@
       <c r="U395" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="396" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W395" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="396" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>22</v>
       </c>
@@ -22208,8 +23404,11 @@
       <c r="U396" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="397" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W396" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="397" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>22</v>
       </c>
@@ -22243,8 +23442,11 @@
       <c r="U397" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="398" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W397" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="398" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>22</v>
       </c>
@@ -22290,8 +23492,11 @@
       <c r="U398" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="399" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W398" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="399" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>22</v>
       </c>
@@ -22325,8 +23530,11 @@
       <c r="U399" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="400" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W399" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="400" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>22</v>
       </c>
@@ -22360,8 +23568,11 @@
       <c r="U400" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="401" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W400" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="401" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>22</v>
       </c>
@@ -22410,8 +23621,11 @@
       <c r="U401" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="402" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W401" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="402" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>22</v>
       </c>
@@ -22445,8 +23659,11 @@
       <c r="U402" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="403" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W402" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="403" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>22</v>
       </c>
@@ -22480,8 +23697,11 @@
       <c r="U403" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="404" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W403" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="404" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>22</v>
       </c>
@@ -22527,8 +23747,11 @@
       <c r="U404" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="405" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W404" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="405" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>22</v>
       </c>
@@ -22574,8 +23797,11 @@
       <c r="U405" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="406" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W405" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="406" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>22</v>
       </c>
@@ -22609,8 +23835,11 @@
       <c r="U406" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="407" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W406" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="407" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>22</v>
       </c>
@@ -22656,8 +23885,11 @@
       <c r="U407" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="408" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="W407" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="408" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>22</v>
       </c>
@@ -22691,11 +23923,11 @@
       <c r="U408" t="s">
         <v>50</v>
       </c>
+      <c r="W408" t="s">
+        <v>664</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="X10" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
